--- a/2025/FLORES DE ESTRADA/Junio/EDESUR JUNIO.xlsx
+++ b/2025/FLORES DE ESTRADA/Junio/EDESUR JUNIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2025\FLORES DE ESTRADA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF052AC4-377D-4177-85FF-2FA53B573A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9249D67-79EA-427B-903C-28F49BE80925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataSignature="AMtx7miNZ3Aa6Oth2NTEJUZDCOk7UNfDow=="/>
     </ext>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="69">
   <si>
     <t>EDESUR - VENCIMIENTO 6/11</t>
   </si>
@@ -235,18 +238,21 @@
   <si>
     <t>EDESUR - VENCIMIENTO 14/07</t>
   </si>
+  <si>
+    <t>Total deudores</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="167" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="166" formatCode="0.00;[Red]0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,8 +340,23 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,6 +402,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -553,13 +580,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -567,69 +594,70 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -645,6 +673,7 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,21 +998,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="66"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="67"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -2631,30 +2660,39 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="68"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="66"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="66"/>
+      <c r="M35" s="69"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="72" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
       <c r="H36" s="5"/>
       <c r="J36" s="32"/>
       <c r="L36" s="32"/>
-      <c r="M36" s="33"/>
+      <c r="M36" s="64">
+        <f>+M28+M27</f>
+        <v>5587.9744643999866</v>
+      </c>
       <c r="O36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2667,80 +2705,80 @@
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="70"/>
-      <c r="K39" s="70"/>
-      <c r="L39" s="70"/>
-      <c r="M39" s="70"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="70"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="70"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="71"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
+      <c r="L41" s="71"/>
+      <c r="M41" s="71"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="70"/>
-      <c r="K42" s="70"/>
-      <c r="L42" s="70"/>
-      <c r="M42" s="70"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="71"/>
+      <c r="L42" s="71"/>
+      <c r="M42" s="71"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6612,21 +6650,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="66"/>
+      <c r="A1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="67"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8218,19 +8256,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="68"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="66"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="66"/>
+      <c r="M35" s="69"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
